--- a/UK_CE_Assessment_Workplan_v1.0.xlsx
+++ b/UK_CE_Assessment_Workplan_v1.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M\Documents\Personal\Freelancework\Cyber Native\Workplans\UK CE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M\Documents\Personal\Freelancework\Cyber Native\Workplans\UK CE\Published\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6CED06-B1ED-44BE-B025-EB5B7F8697F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D7F0A9-26BC-48E1-AB9D-EF034B9C083D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" tabRatio="868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" tabRatio="868" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!! LICENSE - READ FIRST !!" sheetId="9" r:id="rId1"/>
@@ -1457,9 +1457,6 @@
     <t>Description of evidence to substantiate a PASS assessment.</t>
   </si>
   <si>
-    <t>v1,0</t>
-  </si>
-  <si>
     <t>Cyber Essentials Assessment Workplan v1.0 - Controls Assessment</t>
   </si>
   <si>
@@ -1552,6 +1549,9 @@
   </si>
   <si>
     <t>This Cyber Essentials Assessment Workplan (the "Workplan") is published by Cyber Native and licensed under the Creative Commons Attribution-NonCommercial-ShareAlike 4.0 International License (CC BY-NC-SA 4.0). By using, adapting, or sharing this Workplan you agree to the conditions set out below.</t>
+  </si>
+  <si>
+    <t>v1.0</t>
   </si>
 </sst>
 </file>
@@ -1563,7 +1563,7 @@
     <numFmt numFmtId="165" formatCode="dd"/>
     <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="52" x14ac:knownFonts="1">
+  <fonts count="51" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1809,12 +1809,6 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF1C3A54"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1F4E79"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2108,7 +2102,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2251,13 +2245,10 @@
     <xf numFmtId="0" fontId="36" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="39" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="38" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2265,25 +2256,25 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="45" fillId="20" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="20" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="20" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="45" fillId="21" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="46" fillId="21" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="21" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="49" fillId="20" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="48" fillId="20" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2292,48 +2283,48 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="20" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="47" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="19" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="20" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="19" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2350,25 +2341,19 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2379,12 +2364,6 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2409,6 +2388,18 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2885,226 +2876,232 @@
   <dimension ref="A1:AA26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="3" style="53" customWidth="1"/>
-    <col min="2" max="2" width="28" style="53" customWidth="1"/>
-    <col min="3" max="3" width="75" style="53" customWidth="1"/>
-    <col min="4" max="4" width="3" style="53" customWidth="1"/>
-    <col min="5" max="27" width="13" style="53" customWidth="1"/>
-    <col min="28" max="16384" width="9.06640625" style="53"/>
+    <col min="1" max="1" width="3" style="52" customWidth="1"/>
+    <col min="2" max="2" width="28" style="52" customWidth="1"/>
+    <col min="3" max="3" width="75" style="52" customWidth="1"/>
+    <col min="4" max="4" width="3" style="52" customWidth="1"/>
+    <col min="5" max="27" width="13" style="52" customWidth="1"/>
+    <col min="28" max="16384" width="9.06640625" style="52"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="1.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="52"/>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="AA1" s="54" t="s">
+      <c r="A1" s="51"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="AA1" s="53" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="54"/>
+      <c r="B2" s="70" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="2" spans="1:27" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="55"/>
-      <c r="B2" s="73" t="s">
+      <c r="C2" s="67"/>
+      <c r="D2" s="54"/>
+      <c r="AA2" s="62" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="54"/>
+      <c r="B3" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="67"/>
+      <c r="D3" s="54"/>
+    </row>
+    <row r="4" spans="1:27" ht="19.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="54"/>
+      <c r="B4" s="72" t="s">
+        <v>492</v>
+      </c>
+      <c r="C4" s="67"/>
+      <c r="D4" s="54"/>
+    </row>
+    <row r="5" spans="1:27" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="55"/>
+      <c r="B5" s="73" t="s">
+        <v>486</v>
+      </c>
+      <c r="C5" s="67"/>
+      <c r="D5" s="55"/>
+    </row>
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="51"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+    </row>
+    <row r="7" spans="1:27" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="54"/>
+      <c r="B7" s="69" t="s">
         <v>475</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="55"/>
-      <c r="AA2" s="63" t="s">
+      <c r="C7" s="67"/>
+      <c r="D7" s="54"/>
+    </row>
+    <row r="8" spans="1:27" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A8" s="56"/>
+      <c r="B8" s="57" t="s">
+        <v>476</v>
+      </c>
+      <c r="C8" s="58" t="s">
+        <v>477</v>
+      </c>
+      <c r="D8" s="56"/>
+    </row>
+    <row r="9" spans="1:27" ht="52.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="56"/>
+      <c r="B9" s="66" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="3" spans="1:27" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="55"/>
-      <c r="B3" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="72"/>
-      <c r="D3" s="55"/>
-    </row>
-    <row r="4" spans="1:27" ht="19.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="55"/>
-      <c r="B4" s="75" t="s">
+      <c r="C9" s="67"/>
+      <c r="D9" s="56"/>
+    </row>
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="51"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+    </row>
+    <row r="11" spans="1:27" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="54"/>
+      <c r="B11" s="69" t="s">
+        <v>478</v>
+      </c>
+      <c r="C11" s="67"/>
+      <c r="D11" s="54"/>
+    </row>
+    <row r="12" spans="1:27" ht="64.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="56"/>
+      <c r="B12" s="57" t="s">
+        <v>479</v>
+      </c>
+      <c r="C12" s="58" t="s">
+        <v>480</v>
+      </c>
+      <c r="D12" s="56"/>
+    </row>
+    <row r="13" spans="1:27" ht="94.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="59"/>
+      <c r="B13" s="60" t="s">
+        <v>481</v>
+      </c>
+      <c r="C13" s="61" t="s">
+        <v>487</v>
+      </c>
+      <c r="D13" s="59"/>
+    </row>
+    <row r="14" spans="1:27" ht="109.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="56"/>
+      <c r="B14" s="57" t="s">
+        <v>482</v>
+      </c>
+      <c r="C14" s="58" t="s">
         <v>493</v>
       </c>
-      <c r="C4" s="72"/>
-      <c r="D4" s="55"/>
-    </row>
-    <row r="5" spans="1:27" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="56"/>
-      <c r="B5" s="76" t="s">
-        <v>487</v>
-      </c>
-      <c r="C5" s="72"/>
-      <c r="D5" s="56"/>
-    </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="52"/>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-    </row>
-    <row r="7" spans="1:27" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="55"/>
-      <c r="B7" s="77" t="s">
-        <v>476</v>
-      </c>
-      <c r="C7" s="72"/>
-      <c r="D7" s="55"/>
-    </row>
-    <row r="8" spans="1:27" ht="26.25" x14ac:dyDescent="0.45">
-      <c r="A8" s="57"/>
-      <c r="B8" s="58" t="s">
-        <v>477</v>
-      </c>
-      <c r="C8" s="59" t="s">
-        <v>478</v>
-      </c>
-      <c r="D8" s="57"/>
-    </row>
-    <row r="9" spans="1:27" ht="52.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="57"/>
-      <c r="B9" s="71" t="s">
-        <v>502</v>
-      </c>
-      <c r="C9" s="72"/>
-      <c r="D9" s="57"/>
-    </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="52"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-    </row>
-    <row r="11" spans="1:27" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="55"/>
-      <c r="B11" s="77" t="s">
-        <v>479</v>
-      </c>
-      <c r="C11" s="72"/>
-      <c r="D11" s="55"/>
-    </row>
-    <row r="12" spans="1:27" ht="64.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="57"/>
-      <c r="B12" s="58" t="s">
-        <v>480</v>
-      </c>
-      <c r="C12" s="59" t="s">
-        <v>481</v>
-      </c>
-      <c r="D12" s="57"/>
-    </row>
-    <row r="13" spans="1:27" ht="94.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="60"/>
-      <c r="B13" s="61" t="s">
-        <v>482</v>
-      </c>
-      <c r="C13" s="62" t="s">
+      <c r="D14" s="56"/>
+    </row>
+    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="51"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+    </row>
+    <row r="16" spans="1:27" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="54"/>
+      <c r="B16" s="69" t="s">
+        <v>483</v>
+      </c>
+      <c r="C16" s="67"/>
+      <c r="D16" s="54"/>
+    </row>
+    <row r="17" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="56"/>
+      <c r="B17" s="66" t="s">
+        <v>494</v>
+      </c>
+      <c r="C17" s="67"/>
+      <c r="D17" s="56"/>
+    </row>
+    <row r="18" spans="1:4" ht="94.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="56"/>
+      <c r="B18" s="57" t="s">
+        <v>489</v>
+      </c>
+      <c r="C18" s="63" t="s">
+        <v>491</v>
+      </c>
+      <c r="D18" s="56"/>
+    </row>
+    <row r="19" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="51"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+    </row>
+    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="54"/>
+      <c r="B20" s="69" t="s">
+        <v>484</v>
+      </c>
+      <c r="C20" s="67"/>
+      <c r="D20" s="54"/>
+    </row>
+    <row r="21" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="56"/>
+      <c r="B21" s="66" t="s">
+        <v>495</v>
+      </c>
+      <c r="C21" s="67"/>
+      <c r="D21" s="56"/>
+    </row>
+    <row r="22" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="51"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+    </row>
+    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="54"/>
+      <c r="B23" s="69" t="s">
+        <v>485</v>
+      </c>
+      <c r="C23" s="67"/>
+      <c r="D23" s="54"/>
+    </row>
+    <row r="24" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="56"/>
+      <c r="B24" s="66" t="s">
         <v>488</v>
       </c>
-      <c r="D13" s="60"/>
-    </row>
-    <row r="14" spans="1:27" ht="109.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="57"/>
-      <c r="B14" s="58" t="s">
-        <v>483</v>
-      </c>
-      <c r="C14" s="59" t="s">
-        <v>494</v>
-      </c>
-      <c r="D14" s="57"/>
-    </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="52"/>
-      <c r="B15" s="52"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-    </row>
-    <row r="16" spans="1:27" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="55"/>
-      <c r="B16" s="77" t="s">
-        <v>484</v>
-      </c>
-      <c r="C16" s="72"/>
-      <c r="D16" s="55"/>
-    </row>
-    <row r="17" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="57"/>
-      <c r="B17" s="71" t="s">
-        <v>495</v>
-      </c>
-      <c r="C17" s="72"/>
-      <c r="D17" s="57"/>
-    </row>
-    <row r="18" spans="1:4" ht="94.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="57"/>
-      <c r="B18" s="58" t="s">
+      <c r="C24" s="67"/>
+      <c r="D24" s="56"/>
+    </row>
+    <row r="25" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="51"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+    </row>
+    <row r="26" spans="1:4" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="54"/>
+      <c r="B26" s="68" t="s">
         <v>490</v>
       </c>
-      <c r="C18" s="64" t="s">
-        <v>492</v>
-      </c>
-      <c r="D18" s="57"/>
-    </row>
-    <row r="19" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="52"/>
-      <c r="B19" s="52"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-    </row>
-    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="55"/>
-      <c r="B20" s="77" t="s">
-        <v>485</v>
-      </c>
-      <c r="C20" s="72"/>
-      <c r="D20" s="55"/>
-    </row>
-    <row r="21" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="57"/>
-      <c r="B21" s="71" t="s">
-        <v>496</v>
-      </c>
-      <c r="C21" s="72"/>
-      <c r="D21" s="57"/>
-    </row>
-    <row r="22" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="52"/>
-      <c r="B22" s="52"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-    </row>
-    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="55"/>
-      <c r="B23" s="77" t="s">
-        <v>486</v>
-      </c>
-      <c r="C23" s="72"/>
-      <c r="D23" s="55"/>
-    </row>
-    <row r="24" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="57"/>
-      <c r="B24" s="71" t="s">
-        <v>489</v>
-      </c>
-      <c r="C24" s="72"/>
-      <c r="D24" s="57"/>
-    </row>
-    <row r="25" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="52"/>
-      <c r="B25" s="52"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="52"/>
-    </row>
-    <row r="26" spans="1:4" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="55"/>
-      <c r="B26" s="78" t="s">
-        <v>491</v>
-      </c>
-      <c r="C26" s="72"/>
-      <c r="D26" s="55"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B11:C11"/>
@@ -3113,12 +3110,6 @@
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3137,17 +3128,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="70"/>
+      <c r="B1" s="77"/>
     </row>
     <row r="2" spans="1:2" ht="9.75" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="3" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="67"/>
+      <c r="B3" s="74"/>
     </row>
     <row r="4" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
@@ -3194,15 +3185,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="48" t="s">
-        <v>472</v>
+      <c r="B10" s="3" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -3217,22 +3208,22 @@
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="50">
         <v>46174</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="9.75" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="67" t="s">
+      <c r="A14" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="67"/>
+      <c r="B14" s="74"/>
     </row>
     <row r="15" spans="1:2" ht="79.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="68"/>
+      <c r="B15" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3260,102 +3251,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
     </row>
     <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
     </row>
     <row r="3" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="80" t="s">
+        <v>496</v>
+      </c>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+    </row>
+    <row r="5" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+    </row>
+    <row r="6" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="80" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="80"/>
+      <c r="C6" s="80"/>
+    </row>
+    <row r="8" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="79" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="79"/>
+      <c r="C8" s="79"/>
+    </row>
+    <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="80" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="80"/>
+      <c r="C9" s="80"/>
+    </row>
+    <row r="11" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="79"/>
+      <c r="C11" s="79"/>
+    </row>
+    <row r="12" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="80" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="80"/>
+      <c r="C12" s="80"/>
+    </row>
+    <row r="14" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="79" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="79"/>
+      <c r="C14" s="79"/>
+    </row>
+    <row r="15" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="80" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="80"/>
+      <c r="C15" s="80"/>
+    </row>
+    <row r="17" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="79" t="s">
         <v>497</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-    </row>
-    <row r="5" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-    </row>
-    <row r="6" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="79" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-    </row>
-    <row r="8" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="80" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="80"/>
-      <c r="C8" s="80"/>
-    </row>
-    <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="79" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="79"/>
-      <c r="C9" s="79"/>
-    </row>
-    <row r="11" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="80" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="80"/>
-      <c r="C11" s="80"/>
-    </row>
-    <row r="12" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="79" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="79"/>
-      <c r="C12" s="79"/>
-    </row>
-    <row r="14" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="80" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="80"/>
-      <c r="C14" s="80"/>
-    </row>
-    <row r="15" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="79" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="79"/>
-      <c r="C15" s="79"/>
-    </row>
-    <row r="17" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="80" t="s">
+      <c r="B17" s="79"/>
+      <c r="C17" s="79"/>
+    </row>
+    <row r="18" spans="1:3" ht="160.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="80" t="s">
         <v>498</v>
       </c>
-      <c r="B17" s="80"/>
-      <c r="C17" s="80"/>
-    </row>
-    <row r="18" spans="1:3" ht="160.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="79" t="s">
-        <v>499</v>
-      </c>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
+      <c r="B18" s="80"/>
+      <c r="C18" s="80"/>
     </row>
     <row r="20" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="67" t="s">
+      <c r="A20" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="67"/>
-      <c r="C20" s="67"/>
+      <c r="B20" s="74"/>
+      <c r="C20" s="74"/>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
@@ -3601,11 +3592,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
@@ -3615,6 +3601,11 @@
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3634,22 +3625,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="82" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="83"/>
+      <c r="B1" s="82"/>
     </row>
     <row r="2" spans="1:2" ht="22.35" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="83" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="84"/>
+      <c r="B2" s="83"/>
     </row>
     <row r="4" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="81" t="s">
         <v>464</v>
       </c>
-      <c r="B4" s="82"/>
+      <c r="B4" s="81"/>
     </row>
     <row r="5" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
@@ -3688,10 +3679,10 @@
       <c r="B10" s="3"/>
     </row>
     <row r="12" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="82" t="s">
+      <c r="A12" s="81" t="s">
         <v>465</v>
       </c>
-      <c r="B12" s="82"/>
+      <c r="B12" s="81"/>
     </row>
     <row r="13" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
@@ -3730,10 +3721,10 @@
       <c r="B18" s="3"/>
     </row>
     <row r="20" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="82" t="s">
+      <c r="A20" s="81" t="s">
         <v>466</v>
       </c>
-      <c r="B20" s="82"/>
+      <c r="B20" s="81"/>
     </row>
     <row r="21" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
@@ -3754,10 +3745,10 @@
       <c r="B23" s="3"/>
     </row>
     <row r="25" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="82" t="s">
+      <c r="A25" s="81" t="s">
         <v>467</v>
       </c>
-      <c r="B25" s="82"/>
+      <c r="B25" s="81"/>
     </row>
     <row r="26" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
@@ -3784,10 +3775,10 @@
       <c r="B29" s="3"/>
     </row>
     <row r="31" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="82" t="s">
+      <c r="A31" s="81" t="s">
         <v>468</v>
       </c>
-      <c r="B31" s="82"/>
+      <c r="B31" s="81"/>
     </row>
     <row r="32" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="47" t="s">
@@ -3814,10 +3805,10 @@
       <c r="B35" s="3"/>
     </row>
     <row r="37" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="82" t="s">
+      <c r="A37" s="81" t="s">
         <v>469</v>
       </c>
-      <c r="B37" s="82"/>
+      <c r="B37" s="81"/>
     </row>
     <row r="38" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
@@ -3877,52 +3868,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="85" t="s">
-        <v>473</v>
-      </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
-      <c r="P1" s="85"/>
-      <c r="Q1" s="85"/>
-      <c r="R1" s="85"/>
-      <c r="S1" s="85"/>
-      <c r="T1" s="85"/>
-      <c r="U1" s="85"/>
+      <c r="A1" s="84" t="s">
+        <v>472</v>
+      </c>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
     </row>
     <row r="2" spans="1:21" ht="5.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="86"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="86"/>
-      <c r="M2" s="86"/>
-      <c r="N2" s="86"/>
-      <c r="O2" s="86"/>
-      <c r="P2" s="86"/>
-      <c r="Q2" s="86"/>
-      <c r="R2" s="86"/>
-      <c r="S2" s="86"/>
-      <c r="T2" s="86"/>
-      <c r="U2" s="86"/>
+      <c r="A2" s="85"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
+      <c r="P2" s="85"/>
+      <c r="Q2" s="85"/>
+      <c r="R2" s="85"/>
+      <c r="S2" s="85"/>
+      <c r="T2" s="85"/>
+      <c r="U2" s="85"/>
     </row>
     <row r="3" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="6" t="s">
@@ -5831,25 +5822,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="36.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="82" t="s">
         <v>380</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
     </row>
     <row r="2" spans="1:6" ht="5.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="81" t="s">
         <v>381</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
     </row>
     <row r="4" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
@@ -5888,21 +5879,21 @@
         <f>COUNTIF('Controls Assessment'!N4:N35,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="E5" s="89" t="str">
+      <c r="E5" s="86" t="str">
         <f>IF(COUNTIF('Controls Assessment'!N4:N35,"FAIL")=0,IF(COUNTBLANK('Controls Assessment'!N4:N35)=0,"ELIGIBLE FOR SUBMISSION","ASSESSMENT INCOMPLETE"),"NOT ELIGIBLE - FAILURES PRESENT")</f>
         <v>ASSESSMENT INCOMPLETE</v>
       </c>
-      <c r="F5" s="89"/>
+      <c r="F5" s="86"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="82" t="s">
+      <c r="A7" s="81" t="s">
         <v>387</v>
       </c>
-      <c r="B7" s="82"/>
-      <c r="C7" s="82"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="82"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
@@ -6045,14 +6036,14 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="82" t="s">
+      <c r="A15" s="81" t="s">
         <v>389</v>
       </c>
-      <c r="B15" s="82"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
+      <c r="B15" s="81"/>
+      <c r="C15" s="81"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
     </row>
     <row r="16" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
@@ -6082,14 +6073,14 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="82" t="s">
+      <c r="A20" s="81" t="s">
         <v>393</v>
       </c>
-      <c r="B20" s="82"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82"/>
-      <c r="F20" s="82"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="81"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
     </row>
     <row r="21" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
@@ -6107,14 +6098,14 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="82" t="s">
+      <c r="A23" s="81" t="s">
         <v>396</v>
       </c>
-      <c r="B23" s="82"/>
-      <c r="C23" s="82"/>
-      <c r="D23" s="82"/>
-      <c r="E23" s="82"/>
-      <c r="F23" s="82"/>
+      <c r="B23" s="81"/>
+      <c r="C23" s="81"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="81"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
@@ -6173,24 +6164,24 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="82" t="s">
+      <c r="A32" s="81" t="s">
         <v>399</v>
       </c>
-      <c r="B32" s="82"/>
-      <c r="C32" s="82"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="82"/>
-      <c r="F32" s="82"/>
+      <c r="B32" s="81"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="81"/>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B33" s="88" t="s">
+      <c r="B33" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="88"/>
-      <c r="D33" s="88"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
       <c r="E33" s="1" t="s">
         <v>13</v>
       </c>
@@ -6202,11 +6193,11 @@
       <c r="A34" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="88" t="s">
         <v>127</v>
       </c>
-      <c r="C34" s="87"/>
-      <c r="D34" s="87"/>
+      <c r="C34" s="88"/>
+      <c r="D34" s="88"/>
       <c r="E34" s="11" t="str">
         <f>'Controls Assessment'!N4</f>
         <v/>
@@ -6220,11 +6211,11 @@
       <c r="A35" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B35" s="87" t="s">
+      <c r="B35" s="88" t="s">
         <v>136</v>
       </c>
-      <c r="C35" s="87"/>
-      <c r="D35" s="87"/>
+      <c r="C35" s="88"/>
+      <c r="D35" s="88"/>
       <c r="E35" s="11" t="str">
         <f>'Controls Assessment'!N5</f>
         <v/>
@@ -6238,11 +6229,11 @@
       <c r="A36" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B36" s="87" t="s">
+      <c r="B36" s="88" t="s">
         <v>145</v>
       </c>
-      <c r="C36" s="87"/>
-      <c r="D36" s="87"/>
+      <c r="C36" s="88"/>
+      <c r="D36" s="88"/>
       <c r="E36" s="11" t="str">
         <f>'Controls Assessment'!N6</f>
         <v/>
@@ -6256,11 +6247,11 @@
       <c r="A37" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B37" s="87" t="s">
+      <c r="B37" s="88" t="s">
         <v>153</v>
       </c>
-      <c r="C37" s="87"/>
-      <c r="D37" s="87"/>
+      <c r="C37" s="88"/>
+      <c r="D37" s="88"/>
       <c r="E37" s="11" t="str">
         <f>'Controls Assessment'!N7</f>
         <v/>
@@ -6274,11 +6265,11 @@
       <c r="A38" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B38" s="87" t="s">
+      <c r="B38" s="88" t="s">
         <v>160</v>
       </c>
-      <c r="C38" s="87"/>
-      <c r="D38" s="87"/>
+      <c r="C38" s="88"/>
+      <c r="D38" s="88"/>
       <c r="E38" s="11" t="str">
         <f>'Controls Assessment'!N8</f>
         <v/>
@@ -6292,11 +6283,11 @@
       <c r="A39" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B39" s="87" t="s">
+      <c r="B39" s="88" t="s">
         <v>168</v>
       </c>
-      <c r="C39" s="87"/>
-      <c r="D39" s="87"/>
+      <c r="C39" s="88"/>
+      <c r="D39" s="88"/>
       <c r="E39" s="11" t="str">
         <f>'Controls Assessment'!N9</f>
         <v/>
@@ -6310,11 +6301,11 @@
       <c r="A40" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="B40" s="87" t="s">
+      <c r="B40" s="88" t="s">
         <v>175</v>
       </c>
-      <c r="C40" s="87"/>
-      <c r="D40" s="87"/>
+      <c r="C40" s="88"/>
+      <c r="D40" s="88"/>
       <c r="E40" s="11" t="str">
         <f>'Controls Assessment'!N10</f>
         <v/>
@@ -6328,11 +6319,11 @@
       <c r="A41" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="B41" s="87" t="s">
+      <c r="B41" s="88" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="87"/>
-      <c r="D41" s="87"/>
+      <c r="C41" s="88"/>
+      <c r="D41" s="88"/>
       <c r="E41" s="11" t="str">
         <f>'Controls Assessment'!N11</f>
         <v/>
@@ -6346,11 +6337,11 @@
       <c r="A42" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B42" s="87" t="s">
+      <c r="B42" s="88" t="s">
         <v>193</v>
       </c>
-      <c r="C42" s="87"/>
-      <c r="D42" s="87"/>
+      <c r="C42" s="88"/>
+      <c r="D42" s="88"/>
       <c r="E42" s="11" t="str">
         <f>'Controls Assessment'!N12</f>
         <v/>
@@ -6364,11 +6355,11 @@
       <c r="A43" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="B43" s="87" t="s">
+      <c r="B43" s="88" t="s">
         <v>200</v>
       </c>
-      <c r="C43" s="87"/>
-      <c r="D43" s="87"/>
+      <c r="C43" s="88"/>
+      <c r="D43" s="88"/>
       <c r="E43" s="11" t="str">
         <f>'Controls Assessment'!N13</f>
         <v/>
@@ -6382,11 +6373,11 @@
       <c r="A44" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="B44" s="87" t="s">
+      <c r="B44" s="88" t="s">
         <v>207</v>
       </c>
-      <c r="C44" s="87"/>
-      <c r="D44" s="87"/>
+      <c r="C44" s="88"/>
+      <c r="D44" s="88"/>
       <c r="E44" s="11" t="str">
         <f>'Controls Assessment'!N14</f>
         <v/>
@@ -6400,11 +6391,11 @@
       <c r="A45" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B45" s="87" t="s">
+      <c r="B45" s="88" t="s">
         <v>215</v>
       </c>
-      <c r="C45" s="87"/>
-      <c r="D45" s="87"/>
+      <c r="C45" s="88"/>
+      <c r="D45" s="88"/>
       <c r="E45" s="11" t="str">
         <f>'Controls Assessment'!N15</f>
         <v/>
@@ -6418,11 +6409,11 @@
       <c r="A46" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B46" s="87" t="s">
+      <c r="B46" s="88" t="s">
         <v>222</v>
       </c>
-      <c r="C46" s="87"/>
-      <c r="D46" s="87"/>
+      <c r="C46" s="88"/>
+      <c r="D46" s="88"/>
       <c r="E46" s="11" t="str">
         <f>'Controls Assessment'!N16</f>
         <v/>
@@ -6436,11 +6427,11 @@
       <c r="A47" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="B47" s="87" t="s">
+      <c r="B47" s="88" t="s">
         <v>230</v>
       </c>
-      <c r="C47" s="87"/>
-      <c r="D47" s="87"/>
+      <c r="C47" s="88"/>
+      <c r="D47" s="88"/>
       <c r="E47" s="11" t="str">
         <f>'Controls Assessment'!N17</f>
         <v/>
@@ -6454,11 +6445,11 @@
       <c r="A48" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="B48" s="87" t="s">
+      <c r="B48" s="88" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="87"/>
-      <c r="D48" s="87"/>
+      <c r="C48" s="88"/>
+      <c r="D48" s="88"/>
       <c r="E48" s="11" t="str">
         <f>'Controls Assessment'!N18</f>
         <v/>
@@ -6472,11 +6463,11 @@
       <c r="A49" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="B49" s="87" t="s">
+      <c r="B49" s="88" t="s">
         <v>247</v>
       </c>
-      <c r="C49" s="87"/>
-      <c r="D49" s="87"/>
+      <c r="C49" s="88"/>
+      <c r="D49" s="88"/>
       <c r="E49" s="11" t="str">
         <f>'Controls Assessment'!N19</f>
         <v/>
@@ -6490,11 +6481,11 @@
       <c r="A50" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B50" s="87" t="s">
+      <c r="B50" s="88" t="s">
         <v>256</v>
       </c>
-      <c r="C50" s="87"/>
-      <c r="D50" s="87"/>
+      <c r="C50" s="88"/>
+      <c r="D50" s="88"/>
       <c r="E50" s="11" t="str">
         <f>'Controls Assessment'!N20</f>
         <v/>
@@ -6508,11 +6499,11 @@
       <c r="A51" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="B51" s="87" t="s">
+      <c r="B51" s="88" t="s">
         <v>263</v>
       </c>
-      <c r="C51" s="87"/>
-      <c r="D51" s="87"/>
+      <c r="C51" s="88"/>
+      <c r="D51" s="88"/>
       <c r="E51" s="11" t="str">
         <f>'Controls Assessment'!N21</f>
         <v/>
@@ -6526,11 +6517,11 @@
       <c r="A52" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="B52" s="87" t="s">
+      <c r="B52" s="88" t="s">
         <v>271</v>
       </c>
-      <c r="C52" s="87"/>
-      <c r="D52" s="87"/>
+      <c r="C52" s="88"/>
+      <c r="D52" s="88"/>
       <c r="E52" s="11" t="str">
         <f>'Controls Assessment'!N22</f>
         <v/>
@@ -6544,11 +6535,11 @@
       <c r="A53" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="B53" s="87" t="s">
+      <c r="B53" s="88" t="s">
         <v>280</v>
       </c>
-      <c r="C53" s="87"/>
-      <c r="D53" s="87"/>
+      <c r="C53" s="88"/>
+      <c r="D53" s="88"/>
       <c r="E53" s="11" t="str">
         <f>'Controls Assessment'!N23</f>
         <v/>
@@ -6562,11 +6553,11 @@
       <c r="A54" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="B54" s="87" t="s">
+      <c r="B54" s="88" t="s">
         <v>288</v>
       </c>
-      <c r="C54" s="87"/>
-      <c r="D54" s="87"/>
+      <c r="C54" s="88"/>
+      <c r="D54" s="88"/>
       <c r="E54" s="11" t="str">
         <f>'Controls Assessment'!N24</f>
         <v/>
@@ -6580,11 +6571,11 @@
       <c r="A55" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="B55" s="87" t="s">
+      <c r="B55" s="88" t="s">
         <v>295</v>
       </c>
-      <c r="C55" s="87"/>
-      <c r="D55" s="87"/>
+      <c r="C55" s="88"/>
+      <c r="D55" s="88"/>
       <c r="E55" s="11" t="str">
         <f>'Controls Assessment'!N25</f>
         <v/>
@@ -6598,11 +6589,11 @@
       <c r="A56" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B56" s="87" t="s">
+      <c r="B56" s="88" t="s">
         <v>302</v>
       </c>
-      <c r="C56" s="87"/>
-      <c r="D56" s="87"/>
+      <c r="C56" s="88"/>
+      <c r="D56" s="88"/>
       <c r="E56" s="11" t="str">
         <f>'Controls Assessment'!N26</f>
         <v/>
@@ -6616,11 +6607,11 @@
       <c r="A57" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="B57" s="87" t="s">
+      <c r="B57" s="88" t="s">
         <v>309</v>
       </c>
-      <c r="C57" s="87"/>
-      <c r="D57" s="87"/>
+      <c r="C57" s="88"/>
+      <c r="D57" s="88"/>
       <c r="E57" s="11" t="str">
         <f>'Controls Assessment'!N27</f>
         <v/>
@@ -6634,11 +6625,11 @@
       <c r="A58" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="B58" s="87" t="s">
+      <c r="B58" s="88" t="s">
         <v>317</v>
       </c>
-      <c r="C58" s="87"/>
-      <c r="D58" s="87"/>
+      <c r="C58" s="88"/>
+      <c r="D58" s="88"/>
       <c r="E58" s="11" t="str">
         <f>'Controls Assessment'!N28</f>
         <v/>
@@ -6652,11 +6643,11 @@
       <c r="A59" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="B59" s="87" t="s">
+      <c r="B59" s="88" t="s">
         <v>325</v>
       </c>
-      <c r="C59" s="87"/>
-      <c r="D59" s="87"/>
+      <c r="C59" s="88"/>
+      <c r="D59" s="88"/>
       <c r="E59" s="11" t="str">
         <f>'Controls Assessment'!N29</f>
         <v/>
@@ -6670,11 +6661,11 @@
       <c r="A60" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="B60" s="87" t="s">
+      <c r="B60" s="88" t="s">
         <v>332</v>
       </c>
-      <c r="C60" s="87"/>
-      <c r="D60" s="87"/>
+      <c r="C60" s="88"/>
+      <c r="D60" s="88"/>
       <c r="E60" s="11" t="str">
         <f>'Controls Assessment'!N30</f>
         <v/>
@@ -6688,11 +6679,11 @@
       <c r="A61" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="B61" s="87" t="s">
+      <c r="B61" s="88" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="87"/>
-      <c r="D61" s="87"/>
+      <c r="C61" s="88"/>
+      <c r="D61" s="88"/>
       <c r="E61" s="11" t="str">
         <f>'Controls Assessment'!N31</f>
         <v/>
@@ -6706,11 +6697,11 @@
       <c r="A62" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="B62" s="87" t="s">
+      <c r="B62" s="88" t="s">
         <v>347</v>
       </c>
-      <c r="C62" s="87"/>
-      <c r="D62" s="87"/>
+      <c r="C62" s="88"/>
+      <c r="D62" s="88"/>
       <c r="E62" s="11" t="str">
         <f>'Controls Assessment'!N32</f>
         <v/>
@@ -6724,11 +6715,11 @@
       <c r="A63" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="B63" s="87" t="s">
+      <c r="B63" s="88" t="s">
         <v>357</v>
       </c>
-      <c r="C63" s="87"/>
-      <c r="D63" s="87"/>
+      <c r="C63" s="88"/>
+      <c r="D63" s="88"/>
       <c r="E63" s="11" t="str">
         <f>'Controls Assessment'!N33</f>
         <v/>
@@ -6742,11 +6733,11 @@
       <c r="A64" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="B64" s="87" t="s">
+      <c r="B64" s="88" t="s">
         <v>364</v>
       </c>
-      <c r="C64" s="87"/>
-      <c r="D64" s="87"/>
+      <c r="C64" s="88"/>
+      <c r="D64" s="88"/>
       <c r="E64" s="11" t="str">
         <f>'Controls Assessment'!N34</f>
         <v/>
@@ -6760,11 +6751,11 @@
       <c r="A65" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="B65" s="87" t="s">
+      <c r="B65" s="88" t="s">
         <v>372</v>
       </c>
-      <c r="C65" s="87"/>
-      <c r="D65" s="87"/>
+      <c r="C65" s="88"/>
+      <c r="D65" s="88"/>
       <c r="E65" s="11" t="str">
         <f>'Controls Assessment'!N35</f>
         <v/>
@@ -6776,47 +6767,47 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B59:D59"/>
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="B60:D60"/>
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="B62:D62"/>
     <mergeCell ref="B63:D63"/>
     <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <conditionalFormatting sqref="E34:E65">
     <cfRule type="expression" dxfId="9" priority="2">
@@ -6855,412 +6846,412 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:129" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="89" t="s">
         <v>444</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="102" t="s">
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="97" t="s">
         <v>445</v>
       </c>
-      <c r="L1" s="103"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="103"/>
-      <c r="Q1" s="103"/>
-      <c r="R1" s="103"/>
-      <c r="S1" s="103"/>
-      <c r="T1" s="103"/>
-      <c r="U1" s="103"/>
-      <c r="V1" s="103"/>
-      <c r="W1" s="103"/>
-      <c r="X1" s="103"/>
-      <c r="Y1" s="103"/>
-      <c r="Z1" s="103"/>
-      <c r="AA1" s="103"/>
-      <c r="AB1" s="103"/>
-      <c r="AC1" s="103"/>
-      <c r="AD1" s="103"/>
-      <c r="AE1" s="103"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="104"/>
-      <c r="AH1" s="105" t="s">
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="98"/>
+      <c r="T1" s="98"/>
+      <c r="U1" s="98"/>
+      <c r="V1" s="98"/>
+      <c r="W1" s="98"/>
+      <c r="X1" s="98"/>
+      <c r="Y1" s="98"/>
+      <c r="Z1" s="98"/>
+      <c r="AA1" s="98"/>
+      <c r="AB1" s="98"/>
+      <c r="AC1" s="98"/>
+      <c r="AD1" s="98"/>
+      <c r="AE1" s="98"/>
+      <c r="AF1" s="98"/>
+      <c r="AG1" s="99"/>
+      <c r="AH1" s="100" t="s">
         <v>446</v>
       </c>
-      <c r="AI1" s="106"/>
-      <c r="AJ1" s="106"/>
-      <c r="AK1" s="106"/>
-      <c r="AL1" s="106"/>
-      <c r="AM1" s="106"/>
-      <c r="AN1" s="106"/>
-      <c r="AO1" s="106"/>
-      <c r="AP1" s="106"/>
-      <c r="AQ1" s="106"/>
-      <c r="AR1" s="106"/>
-      <c r="AS1" s="106"/>
-      <c r="AT1" s="106"/>
-      <c r="AU1" s="106"/>
-      <c r="AV1" s="106"/>
-      <c r="AW1" s="106"/>
-      <c r="AX1" s="106"/>
-      <c r="AY1" s="106"/>
-      <c r="AZ1" s="106"/>
-      <c r="BA1" s="106"/>
-      <c r="BB1" s="106"/>
-      <c r="BC1" s="106"/>
-      <c r="BD1" s="106"/>
-      <c r="BE1" s="106"/>
-      <c r="BF1" s="106"/>
-      <c r="BG1" s="106"/>
-      <c r="BH1" s="106"/>
-      <c r="BI1" s="106"/>
-      <c r="BJ1" s="106"/>
-      <c r="BK1" s="106"/>
-      <c r="BL1" s="106"/>
-      <c r="BM1" s="106"/>
-      <c r="BN1" s="106"/>
-      <c r="BO1" s="106"/>
-      <c r="BP1" s="106"/>
-      <c r="BQ1" s="106"/>
-      <c r="BR1" s="106"/>
-      <c r="BS1" s="106"/>
-      <c r="BT1" s="106"/>
-      <c r="BU1" s="106"/>
-      <c r="BV1" s="106"/>
-      <c r="BW1" s="106"/>
-      <c r="BX1" s="106"/>
-      <c r="BY1" s="106"/>
-      <c r="BZ1" s="106"/>
-      <c r="CA1" s="106"/>
-      <c r="CB1" s="106"/>
-      <c r="CC1" s="106"/>
-      <c r="CD1" s="106"/>
-      <c r="CE1" s="106"/>
-      <c r="CF1" s="106"/>
-      <c r="CG1" s="106"/>
-      <c r="CH1" s="106"/>
-      <c r="CI1" s="106"/>
-      <c r="CJ1" s="106"/>
-      <c r="CK1" s="106"/>
-      <c r="CL1" s="106"/>
-      <c r="CM1" s="106"/>
-      <c r="CN1" s="106"/>
-      <c r="CO1" s="106"/>
-      <c r="CP1" s="106"/>
-      <c r="CQ1" s="106"/>
-      <c r="CR1" s="106"/>
-      <c r="CS1" s="106"/>
-      <c r="CT1" s="106"/>
-      <c r="CU1" s="106"/>
-      <c r="CV1" s="106"/>
-      <c r="CW1" s="106"/>
-      <c r="CX1" s="106"/>
-      <c r="CY1" s="106"/>
-      <c r="CZ1" s="106"/>
-      <c r="DA1" s="106"/>
-      <c r="DB1" s="106"/>
-      <c r="DC1" s="106"/>
-      <c r="DD1" s="106"/>
-      <c r="DE1" s="106"/>
-      <c r="DF1" s="106"/>
-      <c r="DG1" s="106"/>
-      <c r="DH1" s="106"/>
-      <c r="DI1" s="106"/>
-      <c r="DJ1" s="106"/>
-      <c r="DK1" s="106"/>
-      <c r="DL1" s="106"/>
-      <c r="DM1" s="106"/>
-      <c r="DN1" s="106"/>
-      <c r="DO1" s="106"/>
-      <c r="DP1" s="106"/>
-      <c r="DQ1" s="106"/>
-      <c r="DR1" s="106"/>
-      <c r="DS1" s="106"/>
-      <c r="DT1" s="106"/>
-      <c r="DU1" s="106"/>
+      <c r="AI1" s="101"/>
+      <c r="AJ1" s="101"/>
+      <c r="AK1" s="101"/>
+      <c r="AL1" s="101"/>
+      <c r="AM1" s="101"/>
+      <c r="AN1" s="101"/>
+      <c r="AO1" s="101"/>
+      <c r="AP1" s="101"/>
+      <c r="AQ1" s="101"/>
+      <c r="AR1" s="101"/>
+      <c r="AS1" s="101"/>
+      <c r="AT1" s="101"/>
+      <c r="AU1" s="101"/>
+      <c r="AV1" s="101"/>
+      <c r="AW1" s="101"/>
+      <c r="AX1" s="101"/>
+      <c r="AY1" s="101"/>
+      <c r="AZ1" s="101"/>
+      <c r="BA1" s="101"/>
+      <c r="BB1" s="101"/>
+      <c r="BC1" s="101"/>
+      <c r="BD1" s="101"/>
+      <c r="BE1" s="101"/>
+      <c r="BF1" s="101"/>
+      <c r="BG1" s="101"/>
+      <c r="BH1" s="101"/>
+      <c r="BI1" s="101"/>
+      <c r="BJ1" s="101"/>
+      <c r="BK1" s="101"/>
+      <c r="BL1" s="101"/>
+      <c r="BM1" s="101"/>
+      <c r="BN1" s="101"/>
+      <c r="BO1" s="101"/>
+      <c r="BP1" s="101"/>
+      <c r="BQ1" s="101"/>
+      <c r="BR1" s="101"/>
+      <c r="BS1" s="101"/>
+      <c r="BT1" s="101"/>
+      <c r="BU1" s="101"/>
+      <c r="BV1" s="101"/>
+      <c r="BW1" s="101"/>
+      <c r="BX1" s="101"/>
+      <c r="BY1" s="101"/>
+      <c r="BZ1" s="101"/>
+      <c r="CA1" s="101"/>
+      <c r="CB1" s="101"/>
+      <c r="CC1" s="101"/>
+      <c r="CD1" s="101"/>
+      <c r="CE1" s="101"/>
+      <c r="CF1" s="101"/>
+      <c r="CG1" s="101"/>
+      <c r="CH1" s="101"/>
+      <c r="CI1" s="101"/>
+      <c r="CJ1" s="101"/>
+      <c r="CK1" s="101"/>
+      <c r="CL1" s="101"/>
+      <c r="CM1" s="101"/>
+      <c r="CN1" s="101"/>
+      <c r="CO1" s="101"/>
+      <c r="CP1" s="101"/>
+      <c r="CQ1" s="101"/>
+      <c r="CR1" s="101"/>
+      <c r="CS1" s="101"/>
+      <c r="CT1" s="101"/>
+      <c r="CU1" s="101"/>
+      <c r="CV1" s="101"/>
+      <c r="CW1" s="101"/>
+      <c r="CX1" s="101"/>
+      <c r="CY1" s="101"/>
+      <c r="CZ1" s="101"/>
+      <c r="DA1" s="101"/>
+      <c r="DB1" s="101"/>
+      <c r="DC1" s="101"/>
+      <c r="DD1" s="101"/>
+      <c r="DE1" s="101"/>
+      <c r="DF1" s="101"/>
+      <c r="DG1" s="101"/>
+      <c r="DH1" s="101"/>
+      <c r="DI1" s="101"/>
+      <c r="DJ1" s="101"/>
+      <c r="DK1" s="101"/>
+      <c r="DL1" s="101"/>
+      <c r="DM1" s="101"/>
+      <c r="DN1" s="101"/>
+      <c r="DO1" s="101"/>
+      <c r="DP1" s="101"/>
+      <c r="DQ1" s="101"/>
+      <c r="DR1" s="101"/>
+      <c r="DS1" s="101"/>
+      <c r="DT1" s="101"/>
+      <c r="DU1" s="101"/>
     </row>
     <row r="2" spans="1:129" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="49"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="91" t="s">
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="104" t="s">
         <v>447</v>
       </c>
-      <c r="E2" s="92"/>
-      <c r="F2" s="50">
+      <c r="E2" s="105"/>
+      <c r="F2" s="49">
         <f>IF(ISNUMBER(Cover!B7),Cover!B7+14,DATE(2026,6,22))</f>
         <v>46195</v>
       </c>
-      <c r="G2" s="98" t="s">
+      <c r="G2" s="90" t="s">
         <v>448</v>
       </c>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="94" t="s">
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="91" t="s">
         <v>449</v>
       </c>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="95"/>
-      <c r="T2" s="95"/>
-      <c r="U2" s="95"/>
-      <c r="V2" s="95"/>
-      <c r="W2" s="95"/>
-      <c r="X2" s="95"/>
-      <c r="Y2" s="95"/>
-      <c r="Z2" s="95"/>
-      <c r="AA2" s="95"/>
-      <c r="AB2" s="95"/>
-      <c r="AC2" s="95"/>
-      <c r="AD2" s="95"/>
-      <c r="AE2" s="95"/>
-      <c r="AF2" s="95"/>
-      <c r="AG2" s="96"/>
-      <c r="AH2" s="94" t="s">
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
+      <c r="R2" s="92"/>
+      <c r="S2" s="92"/>
+      <c r="T2" s="92"/>
+      <c r="U2" s="92"/>
+      <c r="V2" s="92"/>
+      <c r="W2" s="92"/>
+      <c r="X2" s="92"/>
+      <c r="Y2" s="92"/>
+      <c r="Z2" s="92"/>
+      <c r="AA2" s="92"/>
+      <c r="AB2" s="92"/>
+      <c r="AC2" s="92"/>
+      <c r="AD2" s="92"/>
+      <c r="AE2" s="92"/>
+      <c r="AF2" s="92"/>
+      <c r="AG2" s="93"/>
+      <c r="AH2" s="91" t="s">
         <v>450</v>
       </c>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="95"/>
-      <c r="AK2" s="95"/>
-      <c r="AL2" s="95"/>
-      <c r="AM2" s="95"/>
-      <c r="AN2" s="95"/>
-      <c r="AO2" s="95"/>
-      <c r="AP2" s="95"/>
-      <c r="AQ2" s="95"/>
-      <c r="AR2" s="95"/>
-      <c r="AS2" s="95"/>
-      <c r="AT2" s="95"/>
-      <c r="AU2" s="95"/>
-      <c r="AV2" s="95"/>
-      <c r="AW2" s="95"/>
-      <c r="AX2" s="95"/>
-      <c r="AY2" s="95"/>
-      <c r="AZ2" s="95"/>
-      <c r="BA2" s="95"/>
-      <c r="BB2" s="95"/>
-      <c r="BC2" s="95"/>
-      <c r="BD2" s="95"/>
-      <c r="BE2" s="95"/>
-      <c r="BF2" s="95"/>
-      <c r="BG2" s="95"/>
-      <c r="BH2" s="95"/>
-      <c r="BI2" s="95"/>
-      <c r="BJ2" s="95"/>
-      <c r="BK2" s="95"/>
-      <c r="BL2" s="96"/>
-      <c r="BM2" s="99" t="s">
+      <c r="AI2" s="92"/>
+      <c r="AJ2" s="92"/>
+      <c r="AK2" s="92"/>
+      <c r="AL2" s="92"/>
+      <c r="AM2" s="92"/>
+      <c r="AN2" s="92"/>
+      <c r="AO2" s="92"/>
+      <c r="AP2" s="92"/>
+      <c r="AQ2" s="92"/>
+      <c r="AR2" s="92"/>
+      <c r="AS2" s="92"/>
+      <c r="AT2" s="92"/>
+      <c r="AU2" s="92"/>
+      <c r="AV2" s="92"/>
+      <c r="AW2" s="92"/>
+      <c r="AX2" s="92"/>
+      <c r="AY2" s="92"/>
+      <c r="AZ2" s="92"/>
+      <c r="BA2" s="92"/>
+      <c r="BB2" s="92"/>
+      <c r="BC2" s="92"/>
+      <c r="BD2" s="92"/>
+      <c r="BE2" s="92"/>
+      <c r="BF2" s="92"/>
+      <c r="BG2" s="92"/>
+      <c r="BH2" s="92"/>
+      <c r="BI2" s="92"/>
+      <c r="BJ2" s="92"/>
+      <c r="BK2" s="92"/>
+      <c r="BL2" s="93"/>
+      <c r="BM2" s="94" t="s">
         <v>451</v>
       </c>
-      <c r="BN2" s="100"/>
-      <c r="BO2" s="100"/>
-      <c r="BP2" s="100"/>
-      <c r="BQ2" s="100"/>
-      <c r="BR2" s="100"/>
-      <c r="BS2" s="100"/>
-      <c r="BT2" s="100"/>
-      <c r="BU2" s="100"/>
-      <c r="BV2" s="100"/>
-      <c r="BW2" s="100"/>
-      <c r="BX2" s="100"/>
-      <c r="BY2" s="100"/>
-      <c r="BZ2" s="100"/>
-      <c r="CA2" s="100"/>
-      <c r="CB2" s="100"/>
-      <c r="CC2" s="100"/>
-      <c r="CD2" s="100"/>
-      <c r="CE2" s="100"/>
-      <c r="CF2" s="100"/>
-      <c r="CG2" s="100"/>
-      <c r="CH2" s="100"/>
-      <c r="CI2" s="100"/>
-      <c r="CJ2" s="100"/>
-      <c r="CK2" s="100"/>
-      <c r="CL2" s="100"/>
-      <c r="CM2" s="100"/>
-      <c r="CN2" s="100"/>
-      <c r="CO2" s="100"/>
-      <c r="CP2" s="100"/>
-      <c r="CQ2" s="101"/>
-      <c r="CR2" s="94" t="s">
+      <c r="BN2" s="95"/>
+      <c r="BO2" s="95"/>
+      <c r="BP2" s="95"/>
+      <c r="BQ2" s="95"/>
+      <c r="BR2" s="95"/>
+      <c r="BS2" s="95"/>
+      <c r="BT2" s="95"/>
+      <c r="BU2" s="95"/>
+      <c r="BV2" s="95"/>
+      <c r="BW2" s="95"/>
+      <c r="BX2" s="95"/>
+      <c r="BY2" s="95"/>
+      <c r="BZ2" s="95"/>
+      <c r="CA2" s="95"/>
+      <c r="CB2" s="95"/>
+      <c r="CC2" s="95"/>
+      <c r="CD2" s="95"/>
+      <c r="CE2" s="95"/>
+      <c r="CF2" s="95"/>
+      <c r="CG2" s="95"/>
+      <c r="CH2" s="95"/>
+      <c r="CI2" s="95"/>
+      <c r="CJ2" s="95"/>
+      <c r="CK2" s="95"/>
+      <c r="CL2" s="95"/>
+      <c r="CM2" s="95"/>
+      <c r="CN2" s="95"/>
+      <c r="CO2" s="95"/>
+      <c r="CP2" s="95"/>
+      <c r="CQ2" s="96"/>
+      <c r="CR2" s="91" t="s">
         <v>452</v>
       </c>
-      <c r="CS2" s="95"/>
-      <c r="CT2" s="95"/>
-      <c r="CU2" s="95"/>
-      <c r="CV2" s="95"/>
-      <c r="CW2" s="95"/>
-      <c r="CX2" s="95"/>
-      <c r="CY2" s="95"/>
-      <c r="CZ2" s="95"/>
-      <c r="DA2" s="95"/>
-      <c r="DB2" s="95"/>
-      <c r="DC2" s="95"/>
-      <c r="DD2" s="95"/>
-      <c r="DE2" s="95"/>
-      <c r="DF2" s="95"/>
-      <c r="DG2" s="95"/>
-      <c r="DH2" s="95"/>
-      <c r="DI2" s="95"/>
-      <c r="DJ2" s="95"/>
-      <c r="DK2" s="95"/>
-      <c r="DL2" s="95"/>
-      <c r="DM2" s="95"/>
-      <c r="DN2" s="95"/>
-      <c r="DO2" s="95"/>
-      <c r="DP2" s="95"/>
-      <c r="DQ2" s="95"/>
-      <c r="DR2" s="95"/>
-      <c r="DS2" s="95"/>
-      <c r="DT2" s="95"/>
-      <c r="DU2" s="95"/>
+      <c r="CS2" s="92"/>
+      <c r="CT2" s="92"/>
+      <c r="CU2" s="92"/>
+      <c r="CV2" s="92"/>
+      <c r="CW2" s="92"/>
+      <c r="CX2" s="92"/>
+      <c r="CY2" s="92"/>
+      <c r="CZ2" s="92"/>
+      <c r="DA2" s="92"/>
+      <c r="DB2" s="92"/>
+      <c r="DC2" s="92"/>
+      <c r="DD2" s="92"/>
+      <c r="DE2" s="92"/>
+      <c r="DF2" s="92"/>
+      <c r="DG2" s="92"/>
+      <c r="DH2" s="92"/>
+      <c r="DI2" s="92"/>
+      <c r="DJ2" s="92"/>
+      <c r="DK2" s="92"/>
+      <c r="DL2" s="92"/>
+      <c r="DM2" s="92"/>
+      <c r="DN2" s="92"/>
+      <c r="DO2" s="92"/>
+      <c r="DP2" s="92"/>
+      <c r="DQ2" s="92"/>
+      <c r="DR2" s="92"/>
+      <c r="DS2" s="92"/>
+      <c r="DT2" s="92"/>
+      <c r="DU2" s="92"/>
     </row>
     <row r="3" spans="1:129" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="103" t="s">
         <v>453</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="90"/>
-      <c r="R3" s="90"/>
-      <c r="S3" s="90"/>
-      <c r="T3" s="90"/>
-      <c r="U3" s="90"/>
-      <c r="V3" s="90"/>
-      <c r="W3" s="90"/>
-      <c r="X3" s="90"/>
-      <c r="Y3" s="90"/>
-      <c r="Z3" s="90"/>
-      <c r="AA3" s="90"/>
-      <c r="AB3" s="90"/>
-      <c r="AC3" s="90"/>
-      <c r="AD3" s="90"/>
-      <c r="AE3" s="90"/>
-      <c r="AF3" s="90"/>
-      <c r="AG3" s="90"/>
-      <c r="AH3" s="90"/>
-      <c r="AI3" s="90"/>
-      <c r="AJ3" s="90"/>
-      <c r="AK3" s="90"/>
-      <c r="AL3" s="90"/>
-      <c r="AM3" s="90"/>
-      <c r="AN3" s="90"/>
-      <c r="AO3" s="90"/>
-      <c r="AP3" s="90"/>
-      <c r="AQ3" s="90"/>
-      <c r="AR3" s="90"/>
-      <c r="AS3" s="90"/>
-      <c r="AT3" s="90"/>
-      <c r="AU3" s="90"/>
-      <c r="AV3" s="90"/>
-      <c r="AW3" s="90"/>
-      <c r="AX3" s="90"/>
-      <c r="AY3" s="90"/>
-      <c r="AZ3" s="90"/>
-      <c r="BA3" s="90"/>
-      <c r="BB3" s="90"/>
-      <c r="BC3" s="90"/>
-      <c r="BD3" s="90"/>
-      <c r="BE3" s="90"/>
-      <c r="BF3" s="90"/>
-      <c r="BG3" s="90"/>
-      <c r="BH3" s="90"/>
-      <c r="BI3" s="90"/>
-      <c r="BJ3" s="90"/>
-      <c r="BK3" s="90"/>
-      <c r="BL3" s="90"/>
-      <c r="BM3" s="90"/>
-      <c r="BN3" s="90"/>
-      <c r="BO3" s="90"/>
-      <c r="BP3" s="90"/>
-      <c r="BQ3" s="90"/>
-      <c r="BR3" s="90"/>
-      <c r="BS3" s="90"/>
-      <c r="BT3" s="90"/>
-      <c r="BU3" s="90"/>
-      <c r="BV3" s="90"/>
-      <c r="BW3" s="90"/>
-      <c r="BX3" s="90"/>
-      <c r="BY3" s="90"/>
-      <c r="BZ3" s="90"/>
-      <c r="CA3" s="90"/>
-      <c r="CB3" s="90"/>
-      <c r="CC3" s="90"/>
-      <c r="CD3" s="90"/>
-      <c r="CE3" s="90"/>
-      <c r="CF3" s="90"/>
-      <c r="CG3" s="90"/>
-      <c r="CH3" s="90"/>
-      <c r="CI3" s="90"/>
-      <c r="CJ3" s="90"/>
-      <c r="CK3" s="90"/>
-      <c r="CL3" s="90"/>
-      <c r="CM3" s="90"/>
-      <c r="CN3" s="90"/>
-      <c r="CO3" s="90"/>
-      <c r="CP3" s="90"/>
-      <c r="CQ3" s="90"/>
-      <c r="CR3" s="90"/>
-      <c r="CS3" s="90"/>
-      <c r="CT3" s="90"/>
-      <c r="CU3" s="90"/>
-      <c r="CV3" s="90"/>
-      <c r="CW3" s="90"/>
-      <c r="CX3" s="90"/>
-      <c r="CY3" s="90"/>
-      <c r="CZ3" s="90"/>
-      <c r="DA3" s="90"/>
-      <c r="DB3" s="90"/>
-      <c r="DC3" s="90"/>
-      <c r="DD3" s="90"/>
-      <c r="DE3" s="90"/>
-      <c r="DF3" s="90"/>
-      <c r="DG3" s="90"/>
-      <c r="DH3" s="90"/>
-      <c r="DI3" s="90"/>
-      <c r="DJ3" s="90"/>
-      <c r="DK3" s="90"/>
-      <c r="DL3" s="90"/>
-      <c r="DM3" s="90"/>
-      <c r="DN3" s="90"/>
-      <c r="DO3" s="90"/>
-      <c r="DP3" s="90"/>
-      <c r="DQ3" s="90"/>
-      <c r="DR3" s="90"/>
-      <c r="DS3" s="65"/>
-      <c r="DT3" s="65"/>
-      <c r="DU3" s="65"/>
-      <c r="DV3" s="66"/>
-      <c r="DW3" s="66"/>
-      <c r="DX3" s="66"/>
-      <c r="DY3" s="66"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="102"/>
+      <c r="P3" s="102"/>
+      <c r="Q3" s="102"/>
+      <c r="R3" s="102"/>
+      <c r="S3" s="102"/>
+      <c r="T3" s="102"/>
+      <c r="U3" s="102"/>
+      <c r="V3" s="102"/>
+      <c r="W3" s="102"/>
+      <c r="X3" s="102"/>
+      <c r="Y3" s="102"/>
+      <c r="Z3" s="102"/>
+      <c r="AA3" s="102"/>
+      <c r="AB3" s="102"/>
+      <c r="AC3" s="102"/>
+      <c r="AD3" s="102"/>
+      <c r="AE3" s="102"/>
+      <c r="AF3" s="102"/>
+      <c r="AG3" s="102"/>
+      <c r="AH3" s="102"/>
+      <c r="AI3" s="102"/>
+      <c r="AJ3" s="102"/>
+      <c r="AK3" s="102"/>
+      <c r="AL3" s="102"/>
+      <c r="AM3" s="102"/>
+      <c r="AN3" s="102"/>
+      <c r="AO3" s="102"/>
+      <c r="AP3" s="102"/>
+      <c r="AQ3" s="102"/>
+      <c r="AR3" s="102"/>
+      <c r="AS3" s="102"/>
+      <c r="AT3" s="102"/>
+      <c r="AU3" s="102"/>
+      <c r="AV3" s="102"/>
+      <c r="AW3" s="102"/>
+      <c r="AX3" s="102"/>
+      <c r="AY3" s="102"/>
+      <c r="AZ3" s="102"/>
+      <c r="BA3" s="102"/>
+      <c r="BB3" s="102"/>
+      <c r="BC3" s="102"/>
+      <c r="BD3" s="102"/>
+      <c r="BE3" s="102"/>
+      <c r="BF3" s="102"/>
+      <c r="BG3" s="102"/>
+      <c r="BH3" s="102"/>
+      <c r="BI3" s="102"/>
+      <c r="BJ3" s="102"/>
+      <c r="BK3" s="102"/>
+      <c r="BL3" s="102"/>
+      <c r="BM3" s="102"/>
+      <c r="BN3" s="102"/>
+      <c r="BO3" s="102"/>
+      <c r="BP3" s="102"/>
+      <c r="BQ3" s="102"/>
+      <c r="BR3" s="102"/>
+      <c r="BS3" s="102"/>
+      <c r="BT3" s="102"/>
+      <c r="BU3" s="102"/>
+      <c r="BV3" s="102"/>
+      <c r="BW3" s="102"/>
+      <c r="BX3" s="102"/>
+      <c r="BY3" s="102"/>
+      <c r="BZ3" s="102"/>
+      <c r="CA3" s="102"/>
+      <c r="CB3" s="102"/>
+      <c r="CC3" s="102"/>
+      <c r="CD3" s="102"/>
+      <c r="CE3" s="102"/>
+      <c r="CF3" s="102"/>
+      <c r="CG3" s="102"/>
+      <c r="CH3" s="102"/>
+      <c r="CI3" s="102"/>
+      <c r="CJ3" s="102"/>
+      <c r="CK3" s="102"/>
+      <c r="CL3" s="102"/>
+      <c r="CM3" s="102"/>
+      <c r="CN3" s="102"/>
+      <c r="CO3" s="102"/>
+      <c r="CP3" s="102"/>
+      <c r="CQ3" s="102"/>
+      <c r="CR3" s="102"/>
+      <c r="CS3" s="102"/>
+      <c r="CT3" s="102"/>
+      <c r="CU3" s="102"/>
+      <c r="CV3" s="102"/>
+      <c r="CW3" s="102"/>
+      <c r="CX3" s="102"/>
+      <c r="CY3" s="102"/>
+      <c r="CZ3" s="102"/>
+      <c r="DA3" s="102"/>
+      <c r="DB3" s="102"/>
+      <c r="DC3" s="102"/>
+      <c r="DD3" s="102"/>
+      <c r="DE3" s="102"/>
+      <c r="DF3" s="102"/>
+      <c r="DG3" s="102"/>
+      <c r="DH3" s="102"/>
+      <c r="DI3" s="102"/>
+      <c r="DJ3" s="102"/>
+      <c r="DK3" s="102"/>
+      <c r="DL3" s="102"/>
+      <c r="DM3" s="102"/>
+      <c r="DN3" s="102"/>
+      <c r="DO3" s="102"/>
+      <c r="DP3" s="102"/>
+      <c r="DQ3" s="102"/>
+      <c r="DR3" s="102"/>
+      <c r="DS3" s="64"/>
+      <c r="DT3" s="64"/>
+      <c r="DU3" s="64"/>
+      <c r="DV3" s="65"/>
+      <c r="DW3" s="65"/>
+      <c r="DX3" s="65"/>
+      <c r="DY3" s="65"/>
     </row>
     <row r="4" spans="1:129" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="32" t="s">
@@ -8825,6 +8816,23 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="CX3:DD3"/>
+    <mergeCell ref="DE3:DK3"/>
+    <mergeCell ref="DL3:DR3"/>
+    <mergeCell ref="BV3:CB3"/>
+    <mergeCell ref="CC3:CI3"/>
+    <mergeCell ref="CJ3:CP3"/>
+    <mergeCell ref="CQ3:CW3"/>
+    <mergeCell ref="BO3:BU3"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="R3:X3"/>
+    <mergeCell ref="Y3:AE3"/>
+    <mergeCell ref="AF3:AL3"/>
+    <mergeCell ref="AM3:AS3"/>
+    <mergeCell ref="AT3:AZ3"/>
+    <mergeCell ref="BA3:BG3"/>
+    <mergeCell ref="BH3:BN3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="AH2:BL2"/>
@@ -8832,27 +8840,10 @@
     <mergeCell ref="CR2:DU2"/>
     <mergeCell ref="K1:AG1"/>
     <mergeCell ref="AH1:DU1"/>
-    <mergeCell ref="BO3:BU3"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="K3:Q3"/>
-    <mergeCell ref="R3:X3"/>
-    <mergeCell ref="Y3:AE3"/>
-    <mergeCell ref="AF3:AL3"/>
     <mergeCell ref="D2:E2"/>
-    <mergeCell ref="AM3:AS3"/>
-    <mergeCell ref="AT3:AZ3"/>
-    <mergeCell ref="BA3:BG3"/>
-    <mergeCell ref="BH3:BN3"/>
     <mergeCell ref="K2:AG2"/>
-    <mergeCell ref="CX3:DD3"/>
-    <mergeCell ref="DE3:DK3"/>
-    <mergeCell ref="DL3:DR3"/>
-    <mergeCell ref="BV3:CB3"/>
-    <mergeCell ref="CC3:CI3"/>
-    <mergeCell ref="CJ3:CP3"/>
-    <mergeCell ref="CQ3:CW3"/>
   </mergeCells>
-  <phoneticPr fontId="51" type="noConversion"/>
+  <phoneticPr fontId="50" type="noConversion"/>
   <conditionalFormatting sqref="I5:I36">
     <cfRule type="expression" dxfId="5" priority="4">
       <formula>$I5="Not Started"</formula>
@@ -8933,24 +8924,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="106" t="s">
         <v>400</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
     </row>
     <row r="2" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="31" t="s">
@@ -10045,14 +10036,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="98" t="s">
+      <c r="A35" s="90" t="s">
         <v>463</v>
       </c>
-      <c r="B35" s="98"/>
-      <c r="C35" s="98"/>
-      <c r="D35" s="98"/>
-      <c r="E35" s="98"/>
-      <c r="F35" s="98"/>
+      <c r="B35" s="90"/>
+      <c r="C35" s="90"/>
+      <c r="D35" s="90"/>
+      <c r="E35" s="90"/>
+      <c r="F35" s="90"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
